--- a/时间示例.xlsx
+++ b/时间示例.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,13 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>总计：1.67h（1 小时 40 分 5 秒）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/时间示例.xlsx
+++ b/时间示例.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\excel-time-calculator\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D26ADB-0C39-4C5B-B636-CB27C3C3B4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9227" activeTab="2"/>
+    <workbookView xWindow="2076" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -192,15 +199,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="h:mm;@"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,352 +225,28 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -575,251 +254,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -829,61 +266,17 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1168,16 +561,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1205,7 +598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1219,7 +612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1233,7 +626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1247,7 +640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1261,7 +654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1275,7 +668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1289,7 +682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1317,7 +710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1331,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1345,7 +738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1359,7 +752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1373,7 +766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1387,7 +780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1401,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1415,7 +808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1429,7 +822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1443,7 +836,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1457,7 +850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1471,7 +864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1485,7 +878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1499,7 +892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,7 +906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1527,7 +920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,7 +934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1555,7 +948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1569,7 +962,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1583,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
@@ -1597,7 +990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -1611,7 +1004,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -1625,7 +1018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
@@ -1639,7 +1032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -1653,7 +1046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
@@ -1667,7 +1060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>31</v>
       </c>
@@ -1681,7 +1074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -1695,7 +1088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>23</v>
       </c>
@@ -1709,7 +1102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -1723,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1737,7 +1130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -1751,7 +1144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -1765,7 +1158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -1779,7 +1172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
@@ -1793,7 +1186,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
@@ -1807,7 +1200,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>36</v>
       </c>
@@ -1821,7 +1214,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
@@ -1835,7 +1228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -1849,7 +1242,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>34</v>
       </c>
@@ -1863,7 +1256,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>25</v>
       </c>
@@ -1877,7 +1270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>33</v>
       </c>
@@ -1891,7 +1284,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -1905,7 +1298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>38</v>
       </c>
@@ -1919,7 +1312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>39</v>
       </c>
@@ -1933,7 +1326,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>2</v>
       </c>
@@ -1947,7 +1340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>40</v>
       </c>
@@ -1961,7 +1354,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
@@ -1975,7 +1368,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
@@ -1989,7 +1382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>34</v>
       </c>
@@ -2003,7 +1396,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -2017,7 +1410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>42</v>
       </c>
@@ -2031,7 +1424,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>43</v>
       </c>
@@ -2045,7 +1438,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -2059,7 +1452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>44</v>
       </c>
@@ -2073,7 +1466,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>45</v>
       </c>
@@ -2087,7 +1480,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>46</v>
       </c>
@@ -2101,7 +1494,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>47</v>
       </c>
@@ -2115,7 +1508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -2129,7 +1522,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -2143,7 +1536,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
@@ -2157,7 +1550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>48</v>
       </c>
@@ -2171,7 +1564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>49</v>
       </c>
@@ -2185,7 +1578,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>0</v>
       </c>
@@ -2199,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>50</v>
       </c>
@@ -2213,7 +1606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>23</v>
       </c>
@@ -2227,7 +1620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>51</v>
       </c>
@@ -2241,7 +1634,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>52</v>
       </c>
@@ -2255,7 +1648,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>53</v>
       </c>
@@ -2269,7 +1662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>54</v>
       </c>
@@ -2283,7 +1676,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>55</v>
       </c>
@@ -2297,7 +1690,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>44</v>
       </c>
@@ -2311,7 +1704,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>56</v>
       </c>
@@ -2325,35 +1718,320 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E25D17C7-13DC-4BAF-8AFF-10629C1D534D}">
+  <dimension ref="A1:A55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C84"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9"/>
     <col min="3" max="3" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2361,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2369,7 +2047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2377,7 +2055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2385,7 +2063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2393,7 +2071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2401,7 +2079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2409,7 +2087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2417,7 +2095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2425,7 +2103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -2433,7 +2111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2441,7 +2119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2449,7 +2127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2457,7 +2135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2465,7 +2143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2473,7 +2151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2481,7 +2159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2489,7 +2167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2497,7 +2175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -2505,7 +2183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2513,7 +2191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -2521,7 +2199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -2529,7 +2207,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2537,7 +2215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,7 +2223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -2553,7 +2231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -2561,7 +2239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2569,7 +2247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -2577,7 +2255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -2585,7 +2263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
@@ -2593,7 +2271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -2601,7 +2279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -2609,7 +2287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
@@ -2617,7 +2295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -2625,7 +2303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
@@ -2633,7 +2311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>31</v>
       </c>
@@ -2641,7 +2319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -2649,7 +2327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>23</v>
       </c>
@@ -2657,7 +2335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -2665,7 +2343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2673,7 +2351,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -2681,7 +2359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -2689,7 +2367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -2697,7 +2375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
@@ -2705,7 +2383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
@@ -2713,7 +2391,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>36</v>
       </c>
@@ -2721,7 +2399,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2729,7 +2407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -2737,7 +2415,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>34</v>
       </c>
@@ -2745,7 +2423,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>25</v>
       </c>
@@ -2753,7 +2431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>33</v>
       </c>
@@ -2761,7 +2439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -2769,7 +2447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>38</v>
       </c>
@@ -2777,7 +2455,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>39</v>
       </c>
@@ -2785,7 +2463,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>2</v>
       </c>
@@ -2793,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>40</v>
       </c>
@@ -2801,7 +2479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
@@ -2809,7 +2487,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
@@ -2817,7 +2495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>34</v>
       </c>
@@ -2825,7 +2503,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -2833,7 +2511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>42</v>
       </c>
@@ -2841,7 +2519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>43</v>
       </c>
@@ -2849,7 +2527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -2857,7 +2535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>44</v>
       </c>
@@ -2865,7 +2543,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>45</v>
       </c>
@@ -2873,7 +2551,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>46</v>
       </c>
@@ -2881,7 +2559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>47</v>
       </c>
@@ -2889,7 +2567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -2897,7 +2575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -2905,7 +2583,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
@@ -2913,7 +2591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>48</v>
       </c>
@@ -2921,7 +2599,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>49</v>
       </c>
@@ -2929,7 +2607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>0</v>
       </c>
@@ -2937,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>50</v>
       </c>
@@ -2945,7 +2623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>23</v>
       </c>
@@ -2953,7 +2631,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>51</v>
       </c>
@@ -2961,7 +2639,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>52</v>
       </c>
@@ -2969,7 +2647,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>53</v>
       </c>
@@ -2977,7 +2655,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>54</v>
       </c>
@@ -2985,7 +2663,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>55</v>
       </c>
@@ -2993,7 +2671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>44</v>
       </c>
@@ -3001,7 +2679,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>56</v>
       </c>
@@ -3009,31 +2687,30 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="C83" s="3"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="C84" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="G1:J84"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="9"/>
     <col min="10" max="10" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:10">
+    <row r="1" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3041,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="7:10">
+    <row r="2" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3049,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="7:10">
+    <row r="3" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
@@ -3057,7 +2734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="7:10">
+    <row r="4" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3065,7 +2742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="7:10">
+    <row r="5" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3073,7 +2750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="7:10">
+    <row r="6" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3081,7 +2758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="7:10">
+    <row r="7" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G7" s="1" t="s">
         <v>6</v>
       </c>
@@ -3089,7 +2766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="7:10">
+    <row r="8" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G8" s="1" t="s">
         <v>7</v>
       </c>
@@ -3097,7 +2774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="7:10">
+    <row r="9" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G9" s="1" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +2782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="7:10">
+    <row r="10" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
         <v>9</v>
       </c>
@@ -3113,7 +2790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="7:10">
+    <row r="11" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G11" s="1" t="s">
         <v>10</v>
       </c>
@@ -3121,7 +2798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="7:10">
+    <row r="12" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G12" s="1" t="s">
         <v>11</v>
       </c>
@@ -3129,7 +2806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="7:10">
+    <row r="13" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G13" s="1" t="s">
         <v>12</v>
       </c>
@@ -3137,7 +2814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="7:10">
+    <row r="14" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
@@ -3145,7 +2822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="7:10">
+    <row r="15" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3153,7 +2830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="7:10">
+    <row r="16" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
@@ -3161,7 +2838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="7:10">
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G17" s="1" t="s">
         <v>16</v>
       </c>
@@ -3169,7 +2846,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="7:10">
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G18" s="1" t="s">
         <v>17</v>
       </c>
@@ -3177,7 +2854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="7:10">
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G19" s="1" t="s">
         <v>18</v>
       </c>
@@ -3185,7 +2862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="7:10">
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3193,7 +2870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="7:10">
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G21" s="1" t="s">
         <v>20</v>
       </c>
@@ -3201,7 +2878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="7:10">
+    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G22" s="1" t="s">
         <v>21</v>
       </c>
@@ -3209,7 +2886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="7:10">
+    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G23" s="1" t="s">
         <v>22</v>
       </c>
@@ -3217,7 +2894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="7:10">
+    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G24" s="1" t="s">
         <v>23</v>
       </c>
@@ -3225,7 +2902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="7:10">
+    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G25" s="1" t="s">
         <v>24</v>
       </c>
@@ -3233,7 +2910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="7:10">
+    <row r="26" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G26" s="1" t="s">
         <v>25</v>
       </c>
@@ -3241,7 +2918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="7:10">
+    <row r="27" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G27" s="1" t="s">
         <v>26</v>
       </c>
@@ -3249,7 +2926,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="7:10">
+    <row r="28" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G28" s="1" t="s">
         <v>27</v>
       </c>
@@ -3257,7 +2934,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="7:10">
+    <row r="29" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G29" s="1" t="s">
         <v>28</v>
       </c>
@@ -3265,7 +2942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="7:10">
+    <row r="30" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
@@ -3273,7 +2950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="7:10">
+    <row r="31" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G31" s="1" t="s">
         <v>29</v>
       </c>
@@ -3281,7 +2958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="7:10">
+    <row r="32" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
         <v>18</v>
       </c>
@@ -3289,7 +2966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="7:10">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G33" s="1" t="s">
         <v>30</v>
       </c>
@@ -3297,7 +2974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="7:10">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G34" s="1" t="s">
         <v>4</v>
       </c>
@@ -3305,7 +2982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="7:10">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G35" s="1" t="s">
         <v>31</v>
       </c>
@@ -3313,7 +2990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="7:10">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G36" s="1" t="s">
         <v>31</v>
       </c>
@@ -3321,7 +2998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="7:10">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G37" s="1" t="s">
         <v>32</v>
       </c>
@@ -3329,7 +3006,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="7:10">
+    <row r="38" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G38" s="1" t="s">
         <v>23</v>
       </c>
@@ -3337,7 +3014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="7:10">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G39" s="1" t="s">
         <v>17</v>
       </c>
@@ -3345,7 +3022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="7:10">
+    <row r="40" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,7 +3030,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="7:10">
+    <row r="41" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
@@ -3361,7 +3038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="7:10">
+    <row r="42" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G42" s="1" t="s">
         <v>13</v>
       </c>
@@ -3369,7 +3046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="7:10">
+    <row r="43" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G43" s="1" t="s">
         <v>20</v>
       </c>
@@ -3377,7 +3054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="7:10">
+    <row r="44" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G44" s="1" t="s">
         <v>34</v>
       </c>
@@ -3385,7 +3062,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="7:10">
+    <row r="45" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G45" s="1" t="s">
         <v>35</v>
       </c>
@@ -3393,7 +3070,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="7:10">
+    <row r="46" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G46" s="1" t="s">
         <v>36</v>
       </c>
@@ -3401,7 +3078,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="7:10">
+    <row r="47" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G47" s="1" t="s">
         <v>2</v>
       </c>
@@ -3409,7 +3086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:10">
+    <row r="48" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G48" s="1" t="s">
         <v>37</v>
       </c>
@@ -3417,7 +3094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="7:10">
+    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G49" s="1" t="s">
         <v>34</v>
       </c>
@@ -3425,7 +3102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="7:10">
+    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G50" s="1" t="s">
         <v>25</v>
       </c>
@@ -3433,7 +3110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="7:10">
+    <row r="51" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G51" s="1" t="s">
         <v>33</v>
       </c>
@@ -3441,7 +3118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="7:10">
+    <row r="52" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G52" s="1" t="s">
         <v>19</v>
       </c>
@@ -3449,7 +3126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="7:10">
+    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G53" s="1" t="s">
         <v>38</v>
       </c>
@@ -3457,7 +3134,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="7:10">
+    <row r="54" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G54" s="1" t="s">
         <v>39</v>
       </c>
@@ -3465,7 +3142,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="7:10">
+    <row r="55" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G55" s="1" t="s">
         <v>2</v>
       </c>
@@ -3473,7 +3150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:10">
+    <row r="56" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G56" s="1" t="s">
         <v>40</v>
       </c>
@@ -3481,7 +3158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="7:10">
+    <row r="57" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G57" s="1" t="s">
         <v>41</v>
       </c>
@@ -3489,7 +3166,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="7:10">
+    <row r="58" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G58" s="1" t="s">
         <v>39</v>
       </c>
@@ -3497,7 +3174,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="7:10">
+    <row r="59" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G59" s="1" t="s">
         <v>34</v>
       </c>
@@ -3505,7 +3182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="7:10">
+    <row r="60" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G60" s="1" t="s">
         <v>19</v>
       </c>
@@ -3513,7 +3190,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="7:10">
+    <row r="61" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G61" s="1" t="s">
         <v>42</v>
       </c>
@@ -3521,7 +3198,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="7:10">
+    <row r="62" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G62" s="1" t="s">
         <v>43</v>
       </c>
@@ -3529,7 +3206,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="7:10">
+    <row r="63" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G63" s="1" t="s">
         <v>4</v>
       </c>
@@ -3537,7 +3214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="7:10">
+    <row r="64" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G64" s="1" t="s">
         <v>44</v>
       </c>
@@ -3545,7 +3222,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="7:10">
+    <row r="65" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G65" s="1" t="s">
         <v>45</v>
       </c>
@@ -3553,7 +3230,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="7:10">
+    <row r="66" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G66" s="1" t="s">
         <v>46</v>
       </c>
@@ -3561,7 +3238,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="7:10">
+    <row r="67" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G67" s="1" t="s">
         <v>47</v>
       </c>
@@ -3569,7 +3246,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="7:10">
+    <row r="68" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G68" s="1" t="s">
         <v>36</v>
       </c>
@@ -3577,7 +3254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="7:10">
+    <row r="69" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G69" s="1" t="s">
         <v>45</v>
       </c>
@@ -3585,7 +3262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="7:10">
+    <row r="70" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G70" s="1" t="s">
         <v>9</v>
       </c>
@@ -3593,7 +3270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="7:10">
+    <row r="71" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G71" s="1" t="s">
         <v>48</v>
       </c>
@@ -3601,7 +3278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="7:10">
+    <row r="72" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G72" s="1" t="s">
         <v>49</v>
       </c>
@@ -3609,7 +3286,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="7:10">
+    <row r="73" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G73" s="1" t="s">
         <v>0</v>
       </c>
@@ -3617,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="7:10">
+    <row r="74" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G74" s="1" t="s">
         <v>50</v>
       </c>
@@ -3625,7 +3302,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="7:10">
+    <row r="75" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G75" s="1" t="s">
         <v>23</v>
       </c>
@@ -3633,7 +3310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="7:10">
+    <row r="76" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G76" s="1" t="s">
         <v>51</v>
       </c>
@@ -3641,7 +3318,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="7:10">
+    <row r="77" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G77" s="1" t="s">
         <v>52</v>
       </c>
@@ -3649,7 +3326,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="7:10">
+    <row r="78" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G78" s="1" t="s">
         <v>53</v>
       </c>
@@ -3657,7 +3334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="7:10">
+    <row r="79" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G79" s="1" t="s">
         <v>54</v>
       </c>
@@ -3665,7 +3342,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="7:10">
+    <row r="80" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G80" s="1" t="s">
         <v>55</v>
       </c>
@@ -3673,7 +3350,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="7:10">
+    <row r="81" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G81" s="1" t="s">
         <v>44</v>
       </c>
@@ -3681,7 +3358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="7:10">
+    <row r="82" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G82" s="1" t="s">
         <v>56</v>
       </c>
@@ -3689,16 +3366,16 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="7:10">
+    <row r="83" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G83" s="3"/>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="7:10">
+    <row r="84" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G84" s="3"/>
       <c r="J84" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/时间示例.xlsx
+++ b/时间示例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\excel-time-calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D26ADB-0C39-4C5B-B636-CB27C3C3B4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB004B4-D6D3-4D41-A742-4521CDD82534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2076" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="58">
   <si>
     <t>1:23</t>
   </si>
@@ -194,6 +194,10 @@
   </si>
   <si>
     <t>0:45</t>
+  </si>
+  <si>
+    <t>**</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -203,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +241,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -258,13 +270,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1862,8 +1875,8 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>50</v>
+      <c r="A25" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
